--- a/D_commonSubSequence/grafica.xlsx
+++ b/D_commonSubSequence/grafica.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\commonSubSequence\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\D_commonSubSequence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85813460-3472-418C-84A1-3F31E514F559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EC4823-197D-4A7E-97CF-7756EC8587DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -7648,15 +7648,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>179294</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>156882</xdr:rowOff>
+      <xdr:colOff>80682</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>398369</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>80682</xdr:rowOff>
+      <xdr:colOff>299757</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7950,22 +7950,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -7979,7 +7979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>10</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>12</v>
       </c>
@@ -8007,7 +8007,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>14</v>
       </c>
@@ -8021,7 +8021,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>16</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>18</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>2.2130000000000001</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>20</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>32.631</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>22</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>242.08199999999999</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>24</v>
       </c>
@@ -8092,15 +8092,15 @@
       </c>
       <c r="T11" s="1"/>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="R16" s="2"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>10</v>
       </c>
@@ -8111,7 +8111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>20</v>
       </c>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>30</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>40</v>
       </c>
@@ -8144,7 +8144,7 @@
         <v>1.6679999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>50</v>
       </c>
@@ -8155,7 +8155,7 @@
         <v>199.99700000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>10</v>
       </c>
@@ -8174,7 +8174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>12</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>14</v>
       </c>
@@ -8196,7 +8196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>16</v>
       </c>
@@ -8207,7 +8207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>18</v>
       </c>
@@ -8218,7 +8218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>20</v>
       </c>
@@ -8229,7 +8229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>22</v>
       </c>
@@ -8240,7 +8240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>24</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>26</v>
       </c>
@@ -8262,7 +8262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>28</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>30</v>
       </c>
@@ -8284,7 +8284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>32</v>
       </c>
@@ -8295,7 +8295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>34</v>
       </c>
@@ -8306,7 +8306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>36</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>38</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>40</v>
       </c>
@@ -8339,7 +8339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>42</v>
       </c>
@@ -8350,7 +8350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>44</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
@@ -8372,7 +8372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>50</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>52</v>
       </c>
@@ -8405,7 +8405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>54</v>
       </c>
@@ -8416,7 +8416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>56</v>
       </c>
@@ -8427,7 +8427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>58</v>
       </c>
@@ -8438,7 +8438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>60</v>
       </c>
@@ -8449,7 +8449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>62</v>
       </c>
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>64</v>
       </c>
@@ -8471,7 +8471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>66</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>68</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>70</v>
       </c>
@@ -8504,7 +8504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>72</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>74</v>
       </c>
@@ -8526,7 +8526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>76</v>
       </c>
@@ -8537,7 +8537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>78</v>
       </c>
@@ -8548,7 +8548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>80</v>
       </c>
@@ -8559,7 +8559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>82</v>
       </c>
@@ -8570,7 +8570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>84</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>86</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>88</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>90</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>92</v>
       </c>
@@ -8625,7 +8625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>94</v>
       </c>
@@ -8636,7 +8636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>96</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>98</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>100</v>
       </c>
@@ -8682,13 +8682,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C18BCA93-1AC8-4676-AED4-ED1D70835D3A}">
   <dimension ref="B1:G40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
@@ -8696,7 +8696,7 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -8704,7 +8704,7 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>10</v>
       </c>
@@ -8732,7 +8732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>12</v>
       </c>
@@ -8746,7 +8746,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>14</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>16</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>18</v>
       </c>
@@ -8788,7 +8788,7 @@
         <v>2.2130000000000001</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>20</v>
       </c>
@@ -8802,7 +8802,7 @@
         <v>32.631</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>22</v>
       </c>
@@ -8816,7 +8816,7 @@
         <v>242.08199999999999</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>24</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>2299.0459999999998</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
@@ -8838,7 +8838,7 @@
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>1000</v>
       </c>
@@ -8852,7 +8852,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>2000</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>3000</v>
       </c>
@@ -8880,7 +8880,7 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>4000</v>
       </c>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>5000</v>
       </c>
@@ -8909,7 +8909,7 @@
         <v>0.30499999999999999</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>6000</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>0.44800000000000001</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>7000</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>0.59399999999999997</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>8000</v>
       </c>
@@ -8951,7 +8951,7 @@
         <v>0.77600000000000002</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>9000</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>0.98199999999999998</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>10000</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>1.2270000000000001</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
@@ -8987,7 +8987,7 @@
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>1000</v>
       </c>
@@ -9001,7 +9001,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>2000</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>3000</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>4000</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>5000</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>6000</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>0.127</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>7000</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>0.17100000000000001</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>8000</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>0.22700000000000001</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>9000</v>
       </c>
@@ -9113,7 +9113,7 @@
         <v>0.27200000000000002</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>10000</v>
       </c>

--- a/D_commonSubSequence/grafica.xlsx
+++ b/D_commonSubSequence/grafica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\D_commonSubSequence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EC4823-197D-4A7E-97CF-7756EC8587DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252492AB-3B67-4444-839C-42A740FB7D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
